--- a/business_surveys/043_global_marketing_leadership_survey--business_surveys.xlsx
+++ b/business_surveys/043_global_marketing_leadership_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'transformational',_'label':_'transformational'}</t>
+          <t>transformational</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Transformational', 'label': 'Transformational'}</t>
+          <t>Transformational</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'transactional',_'label':_'transactional'}</t>
+          <t>transactional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Transactional', 'label': 'Transactional'}</t>
+          <t>Transactional</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'none_of_the_above',_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'None of the above', 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'1-5_years',_'label':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': '1-5 years', 'label': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'5-10_years',_'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': '5-10 years', 'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'10+_years',_'label':_'10+_years'}</t>
+          <t>10+_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': '10+ years', 'label': '10+ years'}</t>
+          <t>10+ years</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'none_of_the_above',_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'None of the above', 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'always',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Always', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'sometimes',_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'Sometimes', 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
